--- a/jpcore-r4/develop-kohetest/CodeSystem-jp-observation-bodymeasurement-code-cs.xlsx
+++ b/jpcore-r4/develop-kohetest/CodeSystem-jp-observation-bodymeasurement-code-cs.xlsx
@@ -105,7 +105,7 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS|1.1.0</t>
   </si>
   <si>
     <t>Hierarchy</t>

--- a/jpcore-r4/develop-kohetest/CodeSystem-jp-observation-bodymeasurement-code-cs.xlsx
+++ b/jpcore-r4/develop-kohetest/CodeSystem-jp-observation-bodymeasurement-code-cs.xlsx
@@ -105,7 +105,7 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS</t>
   </si>
   <si>
     <t>Hierarchy</t>
